--- a/stick-world/config/excel/战斗战术.xlsx
+++ b/stick-world/config/excel/战斗战术.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="战术" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="tactics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -436,234 +436,199 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>name_zh</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>cover_priority</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>flank_enabled</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>retreat_threshold</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>fire_discipline</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>autonomy</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#output_dir: combat</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>唯一ID</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>战术名</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>掩体优先级</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>侧翼</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>撤退阈值</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>火力纪律</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>自主度</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>name_zh</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>cover_priority</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>flank_enabled</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>retreat_threshold</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>fire_discipline</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>autonomy</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>tac_aggressive</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>猛攻</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>主动冲击不惜代价</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>loose</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>high</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>唯一ID</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>战术名</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>掩体优先级</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>侧翼</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>撤退阈值</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>火力纪律</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>自主度</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tac_defensive</t>
+          <t>tac_aggressive</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>坚守</t>
+          <t>猛攻</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>固守阵地寸步不退</t>
+          <t>主动冲击不惜代价</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>loose</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>high</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>tight</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>low</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tac_guerrilla</t>
+          <t>tac_defensive</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>游击</t>
+          <t>坚守</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>打了就跑骚扰为主</t>
+          <t>固守阵地寸步不退</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tight</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>low</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>loose</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>high</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tac_balanced</t>
+          <t>tac_guerrilla</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>均衡</t>
+          <t>游击</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>灵活应对战场局势</t>
+          <t>打了就跑骚扰为主</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -673,57 +638,99 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>loose</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>tac_balanced</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>均衡</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>灵活应对战场局势</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>tac_sniper</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>狙击</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>远程优先避近战</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>tight</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>low</t>
         </is>
